--- a/templates/etrade_transactions_template.xlsx
+++ b/templates/etrade_transactions_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Transactions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1025,7 +1025,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>- Transfers, interest, and cash-only rows are ignored.</t>
+          <t>- Online transfers, interest, fees, and other dated cash rows are kept as account activity for the Dashboard's Account Alpha; TRNSFR CASH TO MARGIN moves stay inside the account and are not counted as deposits or withdrawals.</t>
         </is>
       </c>
     </row>
